--- a/AAII_Financials/Quarterly/DLMAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLMAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
   <si>
     <t>DLMAY</t>
   </si>
@@ -656,73 +656,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F7" s="2">
         <v>46054</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45963</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45872</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45781</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45690</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45592</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45501</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45410</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45319</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45228</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45137</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,8 +767,14 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -797,8 +811,14 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +855,14 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +877,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +917,14 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,8 +961,14 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -965,8 +1005,14 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1049,14 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,8 +1068,10 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1054,8 +1108,14 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1092,8 +1152,14 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1174,10 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1146,8 +1214,14 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1184,8 +1258,14 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1222,8 +1302,14 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1260,8 +1346,14 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1298,8 +1390,14 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,8 +1434,14 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1374,8 +1478,14 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1412,8 +1522,14 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1566,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1610,14 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1654,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,8 +1698,14 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1602,8 +1742,14 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1640,8 +1786,14 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,8 +1830,14 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1716,51 +1874,63 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F38" s="2">
         <v>46054</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45963</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45872</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45781</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45690</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45592</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45501</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45410</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45319</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45228</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45137</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1945,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,350 +1963,406 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>601800</v>
+      </c>
+      <c r="F41" s="3">
         <v>244400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>146700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>498000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>166000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>84800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>204000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>196000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>213700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>233300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>526800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>190900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F42" s="3">
         <v>6600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>8700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>6800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>8800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>8500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>6500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>1500</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>23900</v>
+      </c>
+      <c r="F43" s="3">
         <v>28800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>50500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>43900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>30600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>70000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>31500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>25900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>21000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>44100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>25400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>781300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>821900</v>
+      </c>
+      <c r="F44" s="3">
         <v>813300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>841200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>794400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>680600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>636400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>683200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>638600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>648700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>681300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>678500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>688700</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>20700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>9500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>10000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>14200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1195800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1482900</v>
+      </c>
+      <c r="F46" s="3">
         <v>1122100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1067100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1368700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>905300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>830000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>945000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>888700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>907700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>972800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1251500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>999700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>948200</v>
+      </c>
+      <c r="F47" s="3">
         <v>947400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>883400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>864400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>813100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>781900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>779900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>758800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>250500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>237300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>246400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>228200</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2804800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2797400</v>
+      </c>
+      <c r="F48" s="3">
         <v>2695100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2559400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2552800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2317000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2180500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2204400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2197100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2196900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2035700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1952600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1945400</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>704900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>723600</v>
+      </c>
+      <c r="F49" s="3">
         <v>722500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>692000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>702900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>658700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>627700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>654400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>656300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>654600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>665500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>644100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>675900</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2399,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2443,58 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>98600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>92500</v>
+      </c>
+      <c r="F52" s="3">
         <v>66200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>66000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>65900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>66100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>59000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>58800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>58600</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2531,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5831100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6068100</v>
+      </c>
+      <c r="F54" s="3">
         <v>5572300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5281200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5567500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4760100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4479100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4642500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4559600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4009700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3911300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>4094600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3780000</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2597,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,216 +2615,248 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>348900</v>
+      </c>
+      <c r="F57" s="3">
         <v>93500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>349600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>333500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>266700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>81100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>264800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>238200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>233400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>81300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>246100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>234600</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>302200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>558600</v>
+      </c>
+      <c r="F58" s="3">
         <v>572200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>560200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>715900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>374900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>381700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>375500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>189800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>181100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>190200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>544400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>566400</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>38300</v>
+      </c>
+      <c r="F59" s="3">
         <v>117900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>70600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>57500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>48700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>104800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>22100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>18700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>19000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>99200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>40400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>48700</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>770300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>945800</v>
+      </c>
+      <c r="F60" s="3">
         <v>993900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>980400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1107000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>690300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>700800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>662400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>446800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>433500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>503700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>830900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>849700</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3909600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3997100</v>
+      </c>
+      <c r="F61" s="3">
         <v>3405700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3284900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3311400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3029000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2872300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2979500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3159400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3170200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3030100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2931200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2667400</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F62" s="3">
         <v>23600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>5200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3900</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
@@ -2583,8 +2875,14 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2919,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2963,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +3007,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4777600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5058500</v>
+      </c>
+      <c r="F66" s="3">
         <v>4499000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4355000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4512200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3803400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3658100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3734200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3703500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3697400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3628300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3859400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3626100</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3073,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3113,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3157,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3201,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3245,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>39400</v>
+      </c>
+      <c r="F72" s="3">
         <v>95000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-43200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>93600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-155700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-89000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-137300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-136300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-168300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-211800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-281000</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3333,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3377,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3421,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1053500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1009600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1073300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>926200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1055300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>956700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>821000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>908300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>856000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>312300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>283000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>235200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,51 +3509,63 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F80" s="2">
         <v>46054</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45963</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45872</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45781</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45690</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45592</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45501</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45410</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45319</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45228</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45137</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3212,8 +3602,14 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,46 +3624,54 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>65700</v>
+      </c>
+      <c r="F83" s="3">
         <v>59200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>68900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>68400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>65900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>53000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>62300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>64100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>61200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>48100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>57300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>59600</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3708,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3752,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3796,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3840,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3884,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>426500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>282100</v>
+      </c>
+      <c r="F89" s="3">
         <v>431000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>309400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>309600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>228700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>393500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>266900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>305000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>206000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>355300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>266700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>302500</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,46 +3950,54 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-81900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-77700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-67600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-44800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-39700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-28600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-59400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-32700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-29800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-29400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-38100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-90500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-26000</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4034,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +4078,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-45200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-72000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-30000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-194600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>3400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-63600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-36600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-42800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-13600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-24400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-93500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,46 +4144,54 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F96" s="3">
         <v>21400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>20900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>21300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>18500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>17800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>18700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>18500</v>
-      </c>
-      <c r="K96" s="3">
-        <v>14500</v>
-      </c>
-      <c r="L96" s="3">
-        <v>14900</v>
       </c>
       <c r="M96" s="3">
         <v>14500</v>
       </c>
       <c r="N96" s="3">
+        <v>14900</v>
+      </c>
+      <c r="O96" s="3">
+        <v>14500</v>
+      </c>
+      <c r="P96" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4228,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4272,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,46 +4316,58 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-576700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>120600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-266200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-623100</v>
       </c>
-      <c r="F100" s="3">
-        <v>217000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-155100</v>
-      </c>
       <c r="H100" s="3">
+        <v>217100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-155000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-440700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-222000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-277500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-207900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-640200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>171500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-270800</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3906,42 +4404,54 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-240300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>357500</v>
+      </c>
+      <c r="F102" s="3">
         <v>92900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-343700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>332100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>77100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-110800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-15600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-309300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>344700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>300</v>
       </c>
     </row>
